--- a/documentation/user_stories/user_stories.xlsx
+++ b/documentation/user_stories/user_stories.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinashemajero/Library/Mobile Documents/com~apple~CloudDocs/Web Development/Webdevelopment /Project 2/documentation/user_stories/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEC900A-97EA-514E-9DB9-11D2C0A04CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>User story</t>
   </si>
@@ -41,32 +50,111 @@
   </si>
   <si>
     <t>Won't Have</t>
+  </si>
+  <si>
+    <t>US1</t>
+  </si>
+  <si>
+    <t>visitor</t>
+  </si>
+  <si>
+    <t>I want to search for a meal by name</t>
+  </si>
+  <si>
+    <t>So that I can quickly find relevant recipes</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>I want to see an image of the selected meal,</t>
+  </si>
+  <si>
+    <t>So that I know what the finished dish should look like</t>
+  </si>
+  <si>
+    <t>US2</t>
+  </si>
+  <si>
+    <t>US3</t>
+  </si>
+  <si>
+    <t>I want to view a list of ingredients for a recipe,</t>
+  </si>
+  <si>
+    <t>So that I can prepare everything I need before cooking.</t>
+  </si>
+  <si>
+    <t>I want to see step-by-step cooking instructions,</t>
+  </si>
+  <si>
+    <t>So that I can correctly prepare the meal.</t>
+  </si>
+  <si>
+    <t>US4</t>
+  </si>
+  <si>
+    <t>I want to know the category of the recipe (e.g., dessert, main course),</t>
+  </si>
+  <si>
+    <t>So that I can decide if it suits the occasion.</t>
+  </si>
+  <si>
+    <t>US5</t>
+  </si>
+  <si>
+    <t>I want to see the country of origin for a recipe,</t>
+  </si>
+  <si>
+    <t>So that I can learn about its cultural background.</t>
+  </si>
+  <si>
+    <t>US6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -82,27 +170,39 @@
     </fill>
   </fills>
   <borders count="10">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -112,6 +212,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -123,27 +224,39 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -152,9 +265,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -169,46 +284,50 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -398,72 +517,177 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="26.75"/>
-    <col customWidth="1" min="3" max="3" width="49.5"/>
-    <col customWidth="1" min="4" max="4" width="62.88"/>
-    <col customWidth="1" min="5" max="5" width="11.25"/>
-    <col customWidth="1" min="6" max="6" width="10.88"/>
-    <col customWidth="1" min="7" max="7" width="11.0"/>
+    <col min="2" max="2" width="26.6640625" customWidth="1"/>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="9"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -475,6 +699,7 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:H2"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>